--- a/demo/data/остатки-WB-2026-09-27.xlsx
+++ b/demo/data/остатки-WB-2026-09-27.xlsx
@@ -511,7 +511,7 @@
         <v>1</v>
       </c>
       <c r="F2">
-        <v>136</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="F3">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -551,7 +551,7 @@
         <v>1</v>
       </c>
       <c r="F4">
-        <v>112</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -571,7 +571,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>138</v>
+        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -591,7 +591,7 @@
         <v>1</v>
       </c>
       <c r="F6">
-        <v>120</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -611,7 +611,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>80</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -631,7 +631,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>95</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -651,7 +651,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>92</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -671,7 +671,7 @@
         <v>0</v>
       </c>
       <c r="F10">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="F11">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -711,7 +711,7 @@
         <v>0</v>
       </c>
       <c r="F12">
-        <v>82</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -731,7 +731,7 @@
         <v>0</v>
       </c>
       <c r="F13">
-        <v>103</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:6">
